--- a/salidas/mercado.xlsx
+++ b/salidas/mercado.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,24 +433,24 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>sp500</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>tbill_13w</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -449,7 +461,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -460,7 +472,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
@@ -471,7 +483,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -482,7 +494,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -493,7 +505,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
@@ -504,7 +516,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
@@ -515,7 +527,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -526,7 +538,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -537,7 +549,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -548,7 +560,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -559,7 +571,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -570,7 +582,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -581,7 +593,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -592,7 +604,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -603,7 +615,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -614,7 +626,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -625,7 +637,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -636,7 +648,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
@@ -647,7 +659,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -658,7 +670,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -669,7 +681,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -680,7 +692,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -691,7 +703,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -702,7 +714,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -713,7 +725,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -724,7 +736,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -735,7 +747,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -746,7 +758,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -757,7 +769,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -768,7 +780,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -779,7 +791,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -790,7 +802,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -801,7 +813,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -812,7 +824,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -823,7 +835,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
@@ -834,7 +846,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -845,7 +857,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
@@ -856,7 +868,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -867,7 +879,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
@@ -878,7 +890,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -889,7 +901,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -900,7 +912,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -911,7 +923,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -922,7 +934,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -933,7 +945,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -944,7 +956,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -955,7 +967,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -966,7 +978,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
@@ -977,7 +989,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -988,7 +1000,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -999,7 +1011,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1010,7 +1022,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1021,7 +1033,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1032,7 +1044,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1043,7 +1055,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
@@ -1054,7 +1066,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1065,7 +1077,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1076,7 +1088,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1087,7 +1099,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1098,7 +1110,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
@@ -1109,7 +1121,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1120,7 +1132,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
@@ -1131,7 +1143,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1142,7 +1154,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1153,7 +1165,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1164,7 +1176,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1175,7 +1187,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1186,7 +1198,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1197,7 +1209,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -1208,7 +1220,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -1219,7 +1231,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -1230,7 +1242,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -1241,7 +1253,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -1252,7 +1264,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -1263,7 +1275,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -1274,7 +1286,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
@@ -1285,7 +1297,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -1296,7 +1308,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -1307,7 +1319,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -1318,7 +1330,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -1329,7 +1341,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -1340,7 +1352,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -1351,7 +1363,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -1362,7 +1374,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -1373,7 +1385,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -1384,7 +1396,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -1395,7 +1407,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -1406,7 +1418,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -1417,7 +1429,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -1428,7 +1440,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -1439,7 +1451,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -1450,7 +1462,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -1461,7 +1473,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -1472,7 +1484,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -1483,7 +1495,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -1494,7 +1506,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -1505,7 +1517,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -1516,7 +1528,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -1527,7 +1539,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -1538,7 +1550,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -1549,7 +1561,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -1560,7 +1572,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -1571,7 +1583,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -1582,7 +1594,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -1593,7 +1605,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -1604,7 +1616,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -1615,7 +1627,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -1626,7 +1638,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -1637,7 +1649,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -1648,7 +1660,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -1659,7 +1671,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -1670,7 +1682,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -1681,7 +1693,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -1692,7 +1704,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -1703,7 +1715,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -1714,7 +1726,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
@@ -1725,7 +1737,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -1736,7 +1748,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -1747,7 +1759,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -1758,7 +1770,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -1769,7 +1781,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -1780,7 +1792,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -1791,7 +1803,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -1802,7 +1814,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -1813,7 +1825,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -1824,7 +1836,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -1835,7 +1847,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -1846,7 +1858,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -1857,7 +1869,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -1868,7 +1880,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -1879,7 +1891,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -1890,7 +1902,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -1901,7 +1913,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -1912,7 +1924,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -1923,7 +1935,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -1934,7 +1946,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -1945,7 +1957,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -1956,7 +1968,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -1967,7 +1979,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -1978,7 +1990,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -1989,7 +2001,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -2000,7 +2012,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -2011,7 +2023,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -2022,7 +2034,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -2033,7 +2045,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -2044,7 +2056,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -2055,7 +2067,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -2066,7 +2078,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -2077,7 +2089,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -2088,7 +2100,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -2099,7 +2111,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -2110,7 +2122,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -2121,7 +2133,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -2132,7 +2144,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -2143,7 +2155,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -2154,7 +2166,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -2165,7 +2177,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -2176,7 +2188,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -2187,7 +2199,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -2198,7 +2210,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -2209,7 +2221,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -2220,7 +2232,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -2231,7 +2243,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -2242,7 +2254,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -2253,7 +2265,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -2264,7 +2276,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -2275,7 +2287,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -2286,7 +2298,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -2297,7 +2309,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -2308,7 +2320,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -2319,7 +2331,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -2330,7 +2342,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -2341,7 +2353,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -2352,7 +2364,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -2363,7 +2375,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -2374,7 +2386,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -2385,7 +2397,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -2396,7 +2408,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -2407,7 +2419,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -2418,7 +2430,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -2429,7 +2441,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -2440,7 +2452,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -2451,7 +2463,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -2462,7 +2474,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -2473,7 +2485,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -2484,7 +2496,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -2495,7 +2507,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -2506,7 +2518,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -2517,7 +2529,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -2528,7 +2540,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -2539,7 +2551,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -2550,7 +2562,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -2561,7 +2573,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -2572,7 +2584,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -2583,7 +2595,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -2594,7 +2606,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -2605,7 +2617,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -2616,7 +2628,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -2627,7 +2639,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -2638,7 +2650,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -2649,7 +2661,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -2660,7 +2672,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -2671,7 +2683,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -2682,7 +2694,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -2693,7 +2705,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -2704,7 +2716,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -2715,7 +2727,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -2726,7 +2738,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -2737,7 +2749,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -2748,7 +2760,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -2759,7 +2771,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -2770,7 +2782,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -2781,7 +2793,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -2792,7 +2804,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -2803,7 +2815,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -2814,7 +2826,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -2825,7 +2837,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -2836,7 +2848,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -2847,7 +2859,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -2858,7 +2870,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -2869,7 +2881,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -2880,7 +2892,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -2891,7 +2903,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -2902,7 +2914,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -2913,7 +2925,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -2924,7 +2936,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -2935,7 +2947,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -2946,7 +2958,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -2957,7 +2969,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -2968,7 +2980,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -2979,7 +2991,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -2990,7 +3002,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -3001,7 +3013,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -3012,7 +3024,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -3023,7 +3035,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -3034,7 +3046,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -3045,7 +3057,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -3056,7 +3068,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -3067,7 +3079,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -3078,7 +3090,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -3089,7 +3101,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -3100,7 +3112,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -3111,7 +3123,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -3122,7 +3134,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -3133,7 +3145,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -3144,7 +3156,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -3155,7 +3167,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -3166,14 +3178,14 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>7706.02978515625</v>
+        <v>7704.1298828125</v>
       </c>
       <c r="C250" t="n">
-        <v>4.027999877929688</v>
+        <v>4.067999839782715</v>
       </c>
     </row>
   </sheetData>
